--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98720</v>
+        <v>98721</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103868</v>
+        <v>103869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83413</v>
+        <v>83414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98721</v>
+        <v>98722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103869</v>
+        <v>103871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98722</v>
+        <v>98723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103871</v>
+        <v>103872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83414</v>
+        <v>83415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98723</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103872</v>
+        <v>103873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83415</v>
+        <v>83419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103873</v>
+        <v>103879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83419</v>
+        <v>83420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98730</v>
+        <v>98731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103879</v>
+        <v>103880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83420</v>
+        <v>83424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98731</v>
+        <v>98742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103880</v>
+        <v>103891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83424</v>
+        <v>83430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98742</v>
+        <v>98755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103891</v>
+        <v>103904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98755</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103904</v>
+        <v>103905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83430</v>
+        <v>83443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103905</v>
+        <v>103918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136042005</v>
       </c>
       <c r="B2" t="n">
-        <v>83443</v>
+        <v>83444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103918</v>
+        <v>103919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
